--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N63_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>6.401817064103018</v>
       </c>
       <c r="E2" t="n">
-        <v>3.617245654473392</v>
+        <v>3.246725821238561</v>
       </c>
       <c r="F2" t="n">
-        <v>5.766548301678915</v>
+        <v>5.15828799259836</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>21.83389882202336</v>
       </c>
       <c r="E3" t="n">
-        <v>3.617245654473392</v>
+        <v>3.246725821238561</v>
       </c>
       <c r="F3" t="n">
-        <v>5.766548301678915</v>
+        <v>5.15828799259836</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.24631316055069</v>
+        <v>14.09736323972573</v>
       </c>
       <c r="D4" t="n">
-        <v>11.24617108903045</v>
+        <v>12.50690331114568</v>
       </c>
       <c r="E4" t="n">
-        <v>3.617245654473392</v>
+        <v>3.246725821238561</v>
       </c>
       <c r="F4" t="n">
-        <v>5.766548301678915</v>
+        <v>5.15828799259836</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,23 +576,55 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>12.24631316055069</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.24617108903045</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.246725821238561</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.15828799259836</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W0035F0001T0006Z000C1N63.png</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
         <v>14.13929160795702</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>9.806026187796082</v>
       </c>
-      <c r="E5" t="n">
-        <v>3.617245654473392</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.766548301678915</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>3.246725821238561</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.15828799259836</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.85768148463871</v>
+        <v>1.92687324125379</v>
       </c>
       <c r="D2" t="n">
-        <v>6.401817064103018</v>
+        <v>1.040295272916741</v>
       </c>
       <c r="E2" t="n">
-        <v>3.246725821238561</v>
+        <v>0.5275929459512664</v>
       </c>
       <c r="F2" t="n">
-        <v>5.15828799259836</v>
+        <v>0.8382217987972336</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.86012430402319</v>
+        <v>3.389770199403769</v>
       </c>
       <c r="D3" t="n">
-        <v>21.83389882202336</v>
+        <v>3.548008558578797</v>
       </c>
       <c r="E3" t="n">
-        <v>3.246725821238561</v>
+        <v>0.5275929459512664</v>
       </c>
       <c r="F3" t="n">
-        <v>5.15828799259836</v>
+        <v>0.8382217987972336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.09736323972573</v>
+        <v>2.290821526455431</v>
       </c>
       <c r="D4" t="n">
-        <v>12.50690331114568</v>
+        <v>2.032371788061173</v>
       </c>
       <c r="E4" t="n">
-        <v>3.246725821238561</v>
+        <v>0.5275929459512664</v>
       </c>
       <c r="F4" t="n">
-        <v>5.15828799259836</v>
+        <v>0.8382217987972336</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.24631316055069</v>
+        <v>1.990025888589487</v>
       </c>
       <c r="D5" t="n">
-        <v>11.24617108903045</v>
+        <v>1.827502801967448</v>
       </c>
       <c r="E5" t="n">
-        <v>3.246725821238561</v>
+        <v>0.5275929459512664</v>
       </c>
       <c r="F5" t="n">
-        <v>5.15828799259836</v>
+        <v>0.8382217987972336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.13929160795702</v>
+        <v>2.297634886293016</v>
       </c>
       <c r="D6" t="n">
-        <v>9.806026187796082</v>
+        <v>1.593479255516863</v>
       </c>
       <c r="E6" t="n">
-        <v>3.246725821238561</v>
+        <v>0.5275929459512664</v>
       </c>
       <c r="F6" t="n">
-        <v>5.15828799259836</v>
+        <v>0.8382217987972336</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
